--- a/MiniTemplate/Datas/guide.xlsx
+++ b/MiniTemplate/Datas/guide.xlsx
@@ -1,122 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC83049-DC25-4F56-B9A4-690071DC38AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{5A881FEF-E59D-463E-A88F-6DA22265A5AF}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="guide" sheetId="1" r:id="rId1"/>
+    <sheet name="guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>missionId</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>引导 ID</t>
-  </si>
-  <si>
-    <t>关联任务 ID</t>
-  </si>
-  <si>
-    <t>执行步骤</t>
-  </si>
-  <si>
-    <t>引导目标</t>
-  </si>
-  <si>
-    <t>WorkCenter</t>
-  </si>
-  <si>
-    <t>FirstWorkItem</t>
-  </si>
-  <si>
-    <t>MissionButton</t>
-  </si>
-  <si>
-    <t>FirstMissionReward</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,28 +51,88 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -453,143 +432,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BE1BDC-E571-4613-80FB-E29C8CF2318C}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col width="9.109375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="7.88671875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.109375" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.5546875" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.77734375" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>missionId</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>引导 ID</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>关联任务 ID</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>执行步骤</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>引导目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>WorkCenter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>FirstWorkItem</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>MissionButton</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>FirstMissionReward</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>LotteryButton</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>SingleLotteryButton</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>CommunityButton</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>HomeStoreButton</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>SixthHomeStoreTag</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>ThirdHomeStoreItem</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>1000</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>1001</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>1002</v>
-      </c>
-      <c r="C7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>1003</v>
-      </c>
-      <c r="C8">
-        <v>1000</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>HomePurchaseButton</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/guide.xlsx
+++ b/MiniTemplate/Datas/guide.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="guide" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -437,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="9.109375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="7.88671875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.109375" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9.5546875" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="11.77734375" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9.125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="7.875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.125" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.75" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +473,11 @@
           <t>target</t>
         </is>
       </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -500,6 +505,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -527,6 +537,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -552,6 +567,11 @@
       <c r="E4" s="0" t="inlineStr">
         <is>
           <t>引导目标</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>引导提示文案</t>
         </is>
       </c>
     </row>
@@ -570,6 +590,11 @@
           <t>WorkCenter</t>
         </is>
       </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>点击零工中心，开始打零工</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -586,6 +611,11 @@
           <t>FirstWorkItem</t>
         </is>
       </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>接取零工</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="n">
@@ -602,6 +632,11 @@
           <t>MissionButton</t>
         </is>
       </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>点击任务按钮</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="n">
@@ -618,6 +653,11 @@
           <t>FirstMissionReward</t>
         </is>
       </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>领取任务奖励，别忘了后续任务也来这里领奖噢~</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="n">
@@ -634,6 +674,11 @@
           <t>LotteryButton</t>
         </is>
       </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>点击抽奖按钮</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="n">
@@ -650,6 +695,11 @@
           <t>SingleLotteryButton</t>
         </is>
       </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>点击抽取一次</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
@@ -666,6 +716,11 @@
           <t>CommunityButton</t>
         </is>
       </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>点击社区按钮</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -682,6 +737,11 @@
           <t>HomeStoreButton</t>
         </is>
       </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>点击家具店</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
@@ -698,6 +758,11 @@
           <t>SixthHomeStoreTag</t>
         </is>
       </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>选择客厅类</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -714,6 +779,11 @@
           <t>ThirdHomeStoreItem</t>
         </is>
       </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>点击三人沙发</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -728,6 +798,53 @@
       <c r="E15" s="0" t="inlineStr">
         <is>
           <t>HomePurchaseButton</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>点击购买按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HomeButton</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>点击小屋按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HomeSatisfactionDetailButton</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>点击满意度面板</t>
         </is>
       </c>
     </row>

--- a/MiniTemplate/Datas/guide.xlsx
+++ b/MiniTemplate/Datas/guide.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -807,44 +807,107 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="0" t="n">
         <v>1011</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>1003</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>HomeButton</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>点击小屋按钮</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>1012</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="0" t="n">
         <v>1003</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>HomeSatisfactionDetailButton</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>点击满意度面板</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>LotteryButton</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>点击抽奖按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>LotteryPoolSwitchButton</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>点击切换奖池按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="n">
+        <v>1015</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>MysteryWheelPoolButton</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>选择神秘转盘奖池</t>
         </is>
       </c>
     </row>

--- a/MiniTemplate/Datas/guide.xlsx
+++ b/MiniTemplate/Datas/guide.xlsx
@@ -808,43 +808,43 @@
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>1003</v>
+        <v>3005</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>HomeButton</t>
+          <t>MissionButton</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>点击小屋按钮</t>
+          <t>点击任务按钮，查看鹿伯安的委托</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>1003</v>
+        <v>3005</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>HomeSatisfactionDetailButton</t>
+          <t>Mission3005GoButton</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>点击满意度面板</t>
+          <t>点击前往完成，开始文件盖章挑战</t>
         </is>
       </c>
     </row>

--- a/MiniTemplate/Datas/guide.xlsx
+++ b/MiniTemplate/Datas/guide.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -911,6 +911,48 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HomeButton</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>点击小屋按钮，进入你的家</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HomeSatisfactionDetailButton</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>点击查看满意度面板</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
